--- a/downloads/Search-and-Extraction.xlsx
+++ b/downloads/Search-and-Extraction.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="Rbe7045962c5b4be3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank template" sheetId="2" r:id="R46027abcc71c40db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed example" sheetId="3" r:id="Rd0968c743aae4281"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="R9a6a29efa3df4ae2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank template" sheetId="2" r:id="Rd8d4b5c5410d475f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed example" sheetId="3" r:id="Rcc577bf9818140ee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -355,7 +355,7 @@
     </x:row>
     <x:row r="2" ht="47" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>Dental Research AI • Free, editable Excel worksheet • Version 2 • 8 September 2026</x:v>
+        <x:v>Dental Research AI • Free editable worksheet • Version 3 • 9 September 2026</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -392,7 +392,7 @@
         <x:v>1. Read the example</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>Open Completed example. Every study, event, source excerpt, tool record, and action in that sheet is invented for teaching.</x:v>
+        <x:v>Read the Completed example. Published facts are cited to JOP. Proposed plans, practice errors, imagined comments, and AI-use records are labeled teaching exercises; they are not the authors’ original records.</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
         <x:v>Green = example</x:v>
@@ -425,7 +425,7 @@
         <x:v>4. Use this worksheet</x:v>
       </x:c>
       <x:c r="B9" s="4" t="str">
-        <x:v>Duplicate the blank sheet for each search/source record. The example deliberately pairs an unrun clinical search with an ineligible laboratory teaching extract to demonstrate screening.</x:v>
+        <x:v>Keep the unrun discovery query separate from the published review’s actual search flow. Extract one known source per sheet; verify final eligibility against your own protocol.</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
         <x:v>Follow the field guidance</x:v>
@@ -453,12 +453,12 @@
         <x:v>Use approved storage</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="86" customHeight="1">
+    <x:row r="12" ht="150" customHeight="1">
       <x:c r="A12" s="11" t="str">
         <x:v>Sources / limits</x:v>
       </x:c>
       <x:c r="B12" s="4" t="str">
-        <x:v>Search guidance: https://pubmed.ncbi.nlm.nih.gov/help/ ; review reporting: https://www.prisma-statement.org/</x:v>
+        <x:v>Alfaraj A, Limones Á, Ahmad S, Aljubairah F, Albalaw S, Albesher M, et al. Journal of Prosthodontics. 2026;35(2):127–142. Harnessing AI in prosthodontics and implant dentistry: An umbrella review of systematic evidence https://onlinelibrary.wiley.com/doi/full/10.1111/jopr.70091 Methods/Results, PDF pp. 2–4 (journal pp. 128–130); quality and overlap, PDF p. 13 (journal p. 139).</x:v>
       </x:c>
       <x:c r="C12" s="4" t="str">
         <x:v>Recheck current guidance</x:v>
@@ -480,7 +480,7 @@
         <x:v>Calculation legend</x:v>
       </x:c>
       <x:c r="B14" s="4" t="str">
-        <x:v>Yellow cells are editable inputs; green cells on the example sheet contain invented entries. Dark teal total rows, if present, contain formulas. Do not replace formulas with typed totals.</x:v>
+        <x:v>Yellow cells are editable; green example cells contain published facts and clearly labeled teaching entries. Dark teal timing totals contain formulas. Preserve formulas when editing.</x:v>
       </x:c>
       <x:c r="C14" s="4" t="str">
         <x:v>No color-only status codes</x:v>
@@ -722,14 +722,14 @@
   <x:sheetData>
     <x:row r="1" ht="46" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>Example: draft search and source screening</x:v>
+        <x:v>Example: review search and published-source extraction</x:v>
       </x:c>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6"/>
     </x:row>
     <x:row r="2" ht="47" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>COMPLETED EXAMPLE • Entirely hypothetical • Study this example, then complete your own blank sheet.</x:v>
+        <x:v>Published Alfaraj review facts plus an UNRUN teaching search. Search date below is the drafting date.</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -750,12 +750,12 @@
         <x:v>Guidance / reviewer</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="67" customHeight="1">
+    <x:row r="5" ht="69" customHeight="1">
       <x:c r="A5" s="11" t="str">
         <x:v>Question and eligibility</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>In adults receiving a single implant-supported crown, compare digital versus conventional impressions for patient comfort. Final study-design eligibility: TO CONFIRM.</x:v>
+        <x:v>What systematic or umbrella reviews evaluate AI in prosthodontics and implant dentistry? This discovery exercise includes both review types; final systematic-review eligibility would need a protocol.</x:v>
       </x:c>
       <x:c r="C5" s="4" t="str">
         <x:v>Record protocol boundaries</x:v>
@@ -766,18 +766,18 @@
         <x:v>Database / platform</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>PubMed; draft text-word strategy only.</x:v>
+        <x:v>PubMed. Untested draft; source extraction comes from the author-supplied published Alfaraj paper.</x:v>
       </x:c>
       <x:c r="C6" s="4" t="str">
         <x:v>Name platform and interface</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="67" customHeight="1">
+    <x:row r="7" ht="87" customHeight="1">
       <x:c r="A7" s="11" t="str">
         <x:v>Exact query</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>("dental implant"[tiab] OR "dental implants"[tiab] OR "implant-supported"[tiab]) AND ("intraoral scanning"[tiab] OR "digital impression"[tiab] OR "digital impressions"[tiab])</x:v>
+        <x:v>("artificial intelligence"[tiab] OR "machine learning"[tiab] OR "deep learning"[tiab]) AND (prosthodontic*[tiab] OR "implant dentistry"[tiab] OR "dental implants"[tiab]) AND ("systematic review"[tiab] OR "umbrella review"[tiab])</x:v>
       </x:c>
       <x:c r="C7" s="4" t="str">
         <x:v>Preserve exact executed syntax when run</x:v>
@@ -788,7 +788,7 @@
         <x:v>Date drafted / run</x:v>
       </x:c>
       <x:c r="B8" s="15" t="n">
-        <x:v>46273</x:v>
+        <x:v>46274</x:v>
       </x:c>
       <x:c r="C8" s="4" t="str">
         <x:v>Use an Excel date; label draft versus run</x:v>
@@ -805,45 +805,45 @@
         <x:v>Use the status dropdown</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="60" customHeight="1">
+    <x:row r="10" ht="69" customHeight="1">
       <x:c r="A10" s="11" t="str">
         <x:v>Limits and rationale</x:v>
       </x:c>
       <x:c r="B10" s="12" t="str">
-        <x:v>No date or language limit chosen. Test sensitivity before adding a required comfort term; full-text-only outcome mentions may otherwise be missed.</x:v>
+        <x:v>No language/date limit applied in this untested discovery query. Check MeSH, sensitivity, and database translation with a librarian before a reproducible review search.</x:v>
       </x:c>
       <x:c r="C10" s="4" t="str">
         <x:v>Explain every restriction</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="60" customHeight="1">
+    <x:row r="11" ht="69" customHeight="1">
       <x:c r="A11" s="11" t="str">
         <x:v>Results / export reference</x:v>
       </x:c>
       <x:c r="B11" s="12" t="str">
-        <x:v>No search run, result count, or export exists in this example. Do not invent them.</x:v>
+        <x:v>No new search count or export. The original paper’s published flow is separate: 207 retrieved, 186 deduplicated, 21 full texts assessed, 11 reviews included.</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
         <x:v>Record actual count and filename after execution</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="60" customHeight="1">
+    <x:row r="12" ht="69" customHeight="1">
       <x:c r="A12" s="11" t="str">
         <x:v>Verified source identifier</x:v>
       </x:c>
       <x:c r="B12" s="12" t="str">
-        <x:v>TEACH-E1 — fictional extraction practice, independent of the search above.</x:v>
+        <x:v>Alfaraj A et al. Harnessing AI in prosthodontics and implant dentistry: An umbrella review of systematic evidence. J Prosthodont. 2026;35(2):127–142. DOI 10.1111/jopr.70091.</x:v>
       </x:c>
       <x:c r="C12" s="4" t="str">
         <x:v>Use real verified IDs in your project</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="67" customHeight="1">
+    <x:row r="13" ht="60" customHeight="1">
       <x:c r="A13" s="11" t="str">
         <x:v>Source provenance</x:v>
       </x:c>
       <x:c r="B13" s="12" t="str">
-        <x:v>Supplied mock Methods: 10 manufactured dentate casts received both A and B. Mock Table 1: cast-level means A 70 µm, B 62 µm. Mock Discussion: one operator; no patients. This is not a real publication.</x:v>
+        <x:v>Author-supplied PDF; direct JOP page listed on Guide. Values below are published source facts, not simulated search results.</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
         <x:v>URL/file, access rights, and source authenticity</x:v>
@@ -854,7 +854,7 @@
         <x:v>Design / sample / unit</x:v>
       </x:c>
       <x:c r="B14" s="12" t="str">
-        <x:v>Paired in vitro study, 10 manufactured casts; cast is the unit. Three technical scans averaged within cast/device.</x:v>
+        <x:v>Umbrella review: 11 systematic reviews; 281 primary-study citations representing 261 unique studies. These are not patient counts.</x:v>
       </x:c>
       <x:c r="C14" s="4" t="str">
         <x:v>Do not count technical repeats as independent units</x:v>
@@ -865,7 +865,7 @@
         <x:v>Outcome definition / timing</x:v>
       </x:c>
       <x:c r="B15" s="12" t="str">
-        <x:v>Mean absolute surface deviation (µm) from a laboratory reference. Region, reference accuracy, and exact measurement time: NOT REPORTED.</x:v>
+        <x:v>Mapping and narrative synthesis of AI applications. Searches in April 2025; eligible reviews from 1 January 2018 through 30 April 2025.</x:v>
       </x:c>
       <x:c r="C15" s="4" t="str">
         <x:v>Definition, unit, and time point</x:v>
@@ -876,18 +876,18 @@
         <x:v>Estimate</x:v>
       </x:c>
       <x:c r="B16" s="12" t="str">
-        <x:v>A 70 µm; B 62 µm (stipulated teaching values).</x:v>
+        <x:v>AMSTAR 2: 4 high, 1 low, 6 critically low. Overall CCA 0.77%. Tooth-shade task: two reviews of one same primary study, CCA 1.00.</x:v>
       </x:c>
       <x:c r="C16" s="4" t="str">
         <x:v>Copy exactly from source</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="60" customHeight="1">
+    <x:row r="17" ht="69" customHeight="1">
       <x:c r="A17" s="11" t="str">
         <x:v>Uncertainty</x:v>
       </x:c>
       <x:c r="B17" s="12" t="str">
-        <x:v>NOT REPORTED. Do not compute a confidence interval from group means alone.</x:v>
+        <x:v>No across-review pooled clinical effect or corresponding interval; heterogeneity precluded that meta-analysis. Do not combine incompatible performance measures.</x:v>
       </x:c>
       <x:c r="C17" s="4" t="str">
         <x:v>Keep absent uncertainty explicit</x:v>
@@ -898,40 +898,40 @@
         <x:v>Exact source location</x:v>
       </x:c>
       <x:c r="B18" s="12" t="str">
-        <x:v>TEACH-E1 Methods paragraph 1; Table 1; Discussion paragraph 1.</x:v>
+        <x:v>Methods/Results: PDF pp. 2–4 (journal pp. 128–130). Quality and task overlap: PDF p. 13 (journal p. 139).</x:v>
       </x:c>
       <x:c r="C18" s="4" t="str">
         <x:v>Page, paragraph, table, or figure</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="60" customHeight="1">
+    <x:row r="19" ht="69" customHeight="1">
       <x:c r="A19" s="11" t="str">
         <x:v>Limitations / bias notes</x:v>
       </x:c>
       <x:c r="B19" s="12" t="str">
-        <x:v>One operator and manufactured casts; no clinical endpoints. Formal risk-of-bias assessment requires a suitable full report and method.</x:v>
+        <x:v>Quality and independence vary by task. Low overall overlap does not guarantee independent evidence for every application. Retain attribution when citing an included review’s estimate.</x:v>
       </x:c>
       <x:c r="C19" s="4" t="str">
         <x:v>Distinguish reported facts from appraisal</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="67" customHeight="1">
+    <x:row r="20" ht="60" customHeight="1">
       <x:c r="A20" s="11" t="str">
         <x:v>Supported claim</x:v>
       </x:c>
       <x:c r="B20" s="12" t="str">
-        <x:v>B had a lower observed mean deviation in this hypothetical bench sample. This does not establish comfort, crown survival, or statistical significance.</x:v>
+        <x:v>The review maps a heterogeneous AI evidence base with important quality limitations; it does not establish one pooled clinical benefit.</x:v>
       </x:c>
       <x:c r="C20" s="4" t="str">
         <x:v>Stay within the measured design/outcome</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="67" customHeight="1">
+    <x:row r="21" ht="69" customHeight="1">
       <x:c r="A21" s="11" t="str">
         <x:v>Verification / inclusion decision</x:v>
       </x:c>
       <x:c r="B21" s="12" t="str">
-        <x:v>A human should check each field against the source. TEACH-E1 is a laboratory example and does not meet the clinical comfort question above; exclude from that clinical review.</x:v>
+        <x:v>Known source is relevant to the teaching discovery question as an umbrella review. Final inclusion in a new review and a second independent extraction are NOT YET DONE.</x:v>
       </x:c>
       <x:c r="C21" s="4" t="str">
         <x:v>Second extractor and screening decision</x:v>
